--- a/data/demo/Восток бригады.xlsx
+++ b/data/demo/Восток бригады.xlsx
@@ -464,7 +464,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Паперника, д. 7 к 2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -482,7 +486,11 @@
           <t>Ремонт, Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Город Москва, пер.2-й Динамовский, д. 3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,7 +508,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Шкулёва, д. 7А</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,7 +530,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Нижегородская, д. 78 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -536,7 +552,11 @@
           <t>Ремонт, Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Город Москва, б-р.Самаркандский, д. 12</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -554,7 +574,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Сергия Радонежского, д. 10 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -572,7 +596,11 @@
           <t>Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.1-я Машиностроения, д. 4 к 3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -590,7 +618,11 @@
           <t>Ремонт, Аварии</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Город Москва, пер.1-й Басманный, д. 6</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,7 +640,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Город Москва, пр-кт.Волгоградский, д. 157 к 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -626,7 +662,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.4-я Новокузьминская, д. 9 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -644,7 +684,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Авиамоторная, д. 31</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -662,7 +706,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Новорогожская, д. 14 к 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
